--- a/files/temp_files/statement_2026_10.xlsx
+++ b/files/temp_files/statement_2026_10.xlsx
@@ -597,7 +597,7 @@
         <v>35</v>
       </c>
       <c r="C2">
-        <v>60.21</v>
+        <v>-60.21</v>
       </c>
       <c r="D2" t="s">
         <v>59</v>
@@ -611,7 +611,7 @@
         <v>36</v>
       </c>
       <c r="C3">
-        <v>86.11</v>
+        <v>-86.11</v>
       </c>
       <c r="D3" t="s">
         <v>59</v>
@@ -625,7 +625,7 @@
         <v>37</v>
       </c>
       <c r="C4">
-        <v>93.01000000000001</v>
+        <v>-93.01000000000001</v>
       </c>
       <c r="D4" t="s">
         <v>60</v>
@@ -639,7 +639,7 @@
         <v>38</v>
       </c>
       <c r="C5">
-        <v>43.08</v>
+        <v>-43.08</v>
       </c>
       <c r="D5" t="s">
         <v>61</v>
@@ -653,7 +653,7 @@
         <v>37</v>
       </c>
       <c r="C6">
-        <v>93.39</v>
+        <v>-93.39</v>
       </c>
       <c r="D6" t="s">
         <v>60</v>
@@ -667,7 +667,7 @@
         <v>39</v>
       </c>
       <c r="C7">
-        <v>67.33</v>
+        <v>-67.33</v>
       </c>
       <c r="D7" t="s">
         <v>60</v>
@@ -681,7 +681,7 @@
         <v>40</v>
       </c>
       <c r="C8">
-        <v>47.99</v>
+        <v>-47.99</v>
       </c>
       <c r="D8" t="s">
         <v>61</v>
@@ -695,7 +695,7 @@
         <v>38</v>
       </c>
       <c r="C9">
-        <v>34.13</v>
+        <v>-34.13</v>
       </c>
       <c r="D9" t="s">
         <v>61</v>
@@ -709,7 +709,7 @@
         <v>36</v>
       </c>
       <c r="C10">
-        <v>118.2</v>
+        <v>-118.2</v>
       </c>
       <c r="D10" t="s">
         <v>59</v>
@@ -723,7 +723,7 @@
         <v>41</v>
       </c>
       <c r="C11">
-        <v>36</v>
+        <v>-36</v>
       </c>
       <c r="D11" t="s">
         <v>62</v>
@@ -737,7 +737,7 @@
         <v>42</v>
       </c>
       <c r="C12">
-        <v>116.68</v>
+        <v>-116.68</v>
       </c>
       <c r="D12" t="s">
         <v>63</v>
@@ -779,7 +779,7 @@
         <v>45</v>
       </c>
       <c r="C15">
-        <v>125.79</v>
+        <v>-125.79</v>
       </c>
       <c r="D15" t="s">
         <v>62</v>
@@ -793,7 +793,7 @@
         <v>46</v>
       </c>
       <c r="C16">
-        <v>14.5</v>
+        <v>-14.5</v>
       </c>
       <c r="D16" t="s">
         <v>65</v>
@@ -807,7 +807,7 @@
         <v>47</v>
       </c>
       <c r="C17">
-        <v>59.7</v>
+        <v>-59.7</v>
       </c>
       <c r="D17" t="s">
         <v>66</v>
@@ -821,7 +821,7 @@
         <v>48</v>
       </c>
       <c r="C18">
-        <v>32.85</v>
+        <v>-32.85</v>
       </c>
       <c r="D18" t="s">
         <v>65</v>
@@ -835,7 +835,7 @@
         <v>49</v>
       </c>
       <c r="C19">
-        <v>5.41</v>
+        <v>-5.41</v>
       </c>
       <c r="D19" t="s">
         <v>61</v>
@@ -849,7 +849,7 @@
         <v>47</v>
       </c>
       <c r="C20">
-        <v>183.72</v>
+        <v>-183.72</v>
       </c>
       <c r="D20" t="s">
         <v>66</v>
@@ -863,7 +863,7 @@
         <v>47</v>
       </c>
       <c r="C21">
-        <v>105.1</v>
+        <v>-105.1</v>
       </c>
       <c r="D21" t="s">
         <v>66</v>
@@ -877,7 +877,7 @@
         <v>41</v>
       </c>
       <c r="C22">
-        <v>75.95999999999999</v>
+        <v>-75.95999999999999</v>
       </c>
       <c r="D22" t="s">
         <v>62</v>
@@ -891,7 +891,7 @@
         <v>41</v>
       </c>
       <c r="C23">
-        <v>244.47</v>
+        <v>-244.47</v>
       </c>
       <c r="D23" t="s">
         <v>62</v>
@@ -905,7 +905,7 @@
         <v>50</v>
       </c>
       <c r="C24">
-        <v>456.4</v>
+        <v>-456.4</v>
       </c>
       <c r="D24" t="s">
         <v>65</v>
@@ -919,7 +919,7 @@
         <v>37</v>
       </c>
       <c r="C25">
-        <v>33.1</v>
+        <v>-33.1</v>
       </c>
       <c r="D25" t="s">
         <v>60</v>
@@ -947,7 +947,7 @@
         <v>39</v>
       </c>
       <c r="C27">
-        <v>34.78</v>
+        <v>-34.78</v>
       </c>
       <c r="D27" t="s">
         <v>60</v>
@@ -961,7 +961,7 @@
         <v>47</v>
       </c>
       <c r="C28">
-        <v>171.77</v>
+        <v>-171.77</v>
       </c>
       <c r="D28" t="s">
         <v>66</v>
@@ -975,7 +975,7 @@
         <v>46</v>
       </c>
       <c r="C29">
-        <v>216.08</v>
+        <v>-216.08</v>
       </c>
       <c r="D29" t="s">
         <v>65</v>
@@ -989,7 +989,7 @@
         <v>48</v>
       </c>
       <c r="C30">
-        <v>96.26000000000001</v>
+        <v>-96.26000000000001</v>
       </c>
       <c r="D30" t="s">
         <v>65</v>
@@ -1003,7 +1003,7 @@
         <v>48</v>
       </c>
       <c r="C31">
-        <v>328.21</v>
+        <v>-328.21</v>
       </c>
       <c r="D31" t="s">
         <v>65</v>
@@ -1017,7 +1017,7 @@
         <v>39</v>
       </c>
       <c r="C32">
-        <v>46.69</v>
+        <v>-46.69</v>
       </c>
       <c r="D32" t="s">
         <v>60</v>
@@ -1031,7 +1031,7 @@
         <v>50</v>
       </c>
       <c r="C33">
-        <v>248.34</v>
+        <v>-248.34</v>
       </c>
       <c r="D33" t="s">
         <v>65</v>
@@ -1045,7 +1045,7 @@
         <v>51</v>
       </c>
       <c r="C34">
-        <v>386.37</v>
+        <v>-386.37</v>
       </c>
       <c r="D34" t="s">
         <v>63</v>
@@ -1059,7 +1059,7 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>18.81</v>
+        <v>-18.81</v>
       </c>
       <c r="D35" t="s">
         <v>61</v>
@@ -1073,7 +1073,7 @@
         <v>45</v>
       </c>
       <c r="C36">
-        <v>76.70999999999999</v>
+        <v>-76.70999999999999</v>
       </c>
       <c r="D36" t="s">
         <v>62</v>
@@ -1087,7 +1087,7 @@
         <v>51</v>
       </c>
       <c r="C37">
-        <v>525.9299999999999</v>
+        <v>-525.9299999999999</v>
       </c>
       <c r="D37" t="s">
         <v>63</v>
@@ -1115,7 +1115,7 @@
         <v>47</v>
       </c>
       <c r="C39">
-        <v>37.66</v>
+        <v>-37.66</v>
       </c>
       <c r="D39" t="s">
         <v>66</v>
@@ -1129,7 +1129,7 @@
         <v>52</v>
       </c>
       <c r="C40">
-        <v>796.86</v>
+        <v>-796.86</v>
       </c>
       <c r="D40" t="s">
         <v>63</v>
@@ -1143,7 +1143,7 @@
         <v>35</v>
       </c>
       <c r="C41">
-        <v>54.5</v>
+        <v>-54.5</v>
       </c>
       <c r="D41" t="s">
         <v>59</v>
@@ -1157,7 +1157,7 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>151.44</v>
+        <v>-151.44</v>
       </c>
       <c r="D42" t="s">
         <v>66</v>
@@ -1171,7 +1171,7 @@
         <v>37</v>
       </c>
       <c r="C43">
-        <v>98.36</v>
+        <v>-98.36</v>
       </c>
       <c r="D43" t="s">
         <v>60</v>
@@ -1185,7 +1185,7 @@
         <v>39</v>
       </c>
       <c r="C44">
-        <v>11.03</v>
+        <v>-11.03</v>
       </c>
       <c r="D44" t="s">
         <v>60</v>
@@ -1213,7 +1213,7 @@
         <v>35</v>
       </c>
       <c r="C46">
-        <v>136.73</v>
+        <v>-136.73</v>
       </c>
       <c r="D46" t="s">
         <v>59</v>
@@ -1241,7 +1241,7 @@
         <v>41</v>
       </c>
       <c r="C48">
-        <v>146.91</v>
+        <v>-146.91</v>
       </c>
       <c r="D48" t="s">
         <v>62</v>
@@ -1255,7 +1255,7 @@
         <v>53</v>
       </c>
       <c r="C49">
-        <v>59.52</v>
+        <v>-59.52</v>
       </c>
       <c r="D49" t="s">
         <v>60</v>
@@ -1269,7 +1269,7 @@
         <v>42</v>
       </c>
       <c r="C50">
-        <v>353.66</v>
+        <v>-353.66</v>
       </c>
       <c r="D50" t="s">
         <v>63</v>
@@ -1283,7 +1283,7 @@
         <v>51</v>
       </c>
       <c r="C51">
-        <v>177.89</v>
+        <v>-177.89</v>
       </c>
       <c r="D51" t="s">
         <v>63</v>
@@ -1297,7 +1297,7 @@
         <v>41</v>
       </c>
       <c r="C52">
-        <v>73.54000000000001</v>
+        <v>-73.54000000000001</v>
       </c>
       <c r="D52" t="s">
         <v>62</v>
@@ -1311,7 +1311,7 @@
         <v>52</v>
       </c>
       <c r="C53">
-        <v>265.87</v>
+        <v>-265.87</v>
       </c>
       <c r="D53" t="s">
         <v>63</v>
@@ -1325,7 +1325,7 @@
         <v>46</v>
       </c>
       <c r="C54">
-        <v>53.68</v>
+        <v>-53.68</v>
       </c>
       <c r="D54" t="s">
         <v>65</v>
@@ -1339,7 +1339,7 @@
         <v>40</v>
       </c>
       <c r="C55">
-        <v>42.97</v>
+        <v>-42.97</v>
       </c>
       <c r="D55" t="s">
         <v>61</v>
@@ -1367,7 +1367,7 @@
         <v>51</v>
       </c>
       <c r="C57">
-        <v>144.18</v>
+        <v>-144.18</v>
       </c>
       <c r="D57" t="s">
         <v>63</v>
@@ -1381,7 +1381,7 @@
         <v>51</v>
       </c>
       <c r="C58">
-        <v>682.73</v>
+        <v>-682.73</v>
       </c>
       <c r="D58" t="s">
         <v>63</v>
@@ -1395,7 +1395,7 @@
         <v>36</v>
       </c>
       <c r="C59">
-        <v>59.94</v>
+        <v>-59.94</v>
       </c>
       <c r="D59" t="s">
         <v>59</v>
@@ -1409,7 +1409,7 @@
         <v>39</v>
       </c>
       <c r="C60">
-        <v>96.05</v>
+        <v>-96.05</v>
       </c>
       <c r="D60" t="s">
         <v>60</v>
@@ -1423,7 +1423,7 @@
         <v>41</v>
       </c>
       <c r="C61">
-        <v>89.40000000000001</v>
+        <v>-89.40000000000001</v>
       </c>
       <c r="D61" t="s">
         <v>62</v>
@@ -1437,7 +1437,7 @@
         <v>54</v>
       </c>
       <c r="C62">
-        <v>68.72</v>
+        <v>-68.72</v>
       </c>
       <c r="D62" t="s">
         <v>59</v>
@@ -1465,7 +1465,7 @@
         <v>51</v>
       </c>
       <c r="C64">
-        <v>683.7</v>
+        <v>-683.7</v>
       </c>
       <c r="D64" t="s">
         <v>63</v>
@@ -1493,7 +1493,7 @@
         <v>53</v>
       </c>
       <c r="C66">
-        <v>43.37</v>
+        <v>-43.37</v>
       </c>
       <c r="D66" t="s">
         <v>60</v>
@@ -1535,7 +1535,7 @@
         <v>40</v>
       </c>
       <c r="C69">
-        <v>43.62</v>
+        <v>-43.62</v>
       </c>
       <c r="D69" t="s">
         <v>61</v>
@@ -1549,7 +1549,7 @@
         <v>45</v>
       </c>
       <c r="C70">
-        <v>182.52</v>
+        <v>-182.52</v>
       </c>
       <c r="D70" t="s">
         <v>62</v>
@@ -1563,7 +1563,7 @@
         <v>49</v>
       </c>
       <c r="C71">
-        <v>12.01</v>
+        <v>-12.01</v>
       </c>
       <c r="D71" t="s">
         <v>61</v>
@@ -1577,7 +1577,7 @@
         <v>56</v>
       </c>
       <c r="C72">
-        <v>193.27</v>
+        <v>-193.27</v>
       </c>
       <c r="D72" t="s">
         <v>66</v>
@@ -1591,7 +1591,7 @@
         <v>57</v>
       </c>
       <c r="C73">
-        <v>58.79</v>
+        <v>-58.79</v>
       </c>
       <c r="D73" t="s">
         <v>62</v>
@@ -1605,7 +1605,7 @@
         <v>42</v>
       </c>
       <c r="C74">
-        <v>463.41</v>
+        <v>-463.41</v>
       </c>
       <c r="D74" t="s">
         <v>63</v>
@@ -1619,7 +1619,7 @@
         <v>40</v>
       </c>
       <c r="C75">
-        <v>42.67</v>
+        <v>-42.67</v>
       </c>
       <c r="D75" t="s">
         <v>61</v>
@@ -1633,7 +1633,7 @@
         <v>37</v>
       </c>
       <c r="C76">
-        <v>97.84999999999999</v>
+        <v>-97.84999999999999</v>
       </c>
       <c r="D76" t="s">
         <v>60</v>
@@ -1647,7 +1647,7 @@
         <v>58</v>
       </c>
       <c r="C77">
-        <v>97.08</v>
+        <v>-97.08</v>
       </c>
       <c r="D77" t="s">
         <v>66</v>
@@ -1661,7 +1661,7 @@
         <v>35</v>
       </c>
       <c r="C78">
-        <v>146.24</v>
+        <v>-146.24</v>
       </c>
       <c r="D78" t="s">
         <v>59</v>
@@ -1675,7 +1675,7 @@
         <v>53</v>
       </c>
       <c r="C79">
-        <v>40.42</v>
+        <v>-40.42</v>
       </c>
       <c r="D79" t="s">
         <v>60</v>
@@ -1689,7 +1689,7 @@
         <v>35</v>
       </c>
       <c r="C80">
-        <v>122.43</v>
+        <v>-122.43</v>
       </c>
       <c r="D80" t="s">
         <v>59</v>
@@ -1703,7 +1703,7 @@
         <v>56</v>
       </c>
       <c r="C81">
-        <v>85.84999999999999</v>
+        <v>-85.84999999999999</v>
       </c>
       <c r="D81" t="s">
         <v>66</v>
@@ -1717,7 +1717,7 @@
         <v>41</v>
       </c>
       <c r="C82">
-        <v>151.6</v>
+        <v>-151.6</v>
       </c>
       <c r="D82" t="s">
         <v>62</v>
@@ -1731,7 +1731,7 @@
         <v>53</v>
       </c>
       <c r="C83">
-        <v>47.13</v>
+        <v>-47.13</v>
       </c>
       <c r="D83" t="s">
         <v>60</v>
@@ -1745,7 +1745,7 @@
         <v>52</v>
       </c>
       <c r="C84">
-        <v>856.21</v>
+        <v>-856.21</v>
       </c>
       <c r="D84" t="s">
         <v>63</v>
@@ -1759,7 +1759,7 @@
         <v>42</v>
       </c>
       <c r="C85">
-        <v>994.85</v>
+        <v>-994.85</v>
       </c>
       <c r="D85" t="s">
         <v>63</v>
@@ -1773,7 +1773,7 @@
         <v>47</v>
       </c>
       <c r="C86">
-        <v>78.3</v>
+        <v>-78.3</v>
       </c>
       <c r="D86" t="s">
         <v>66</v>
@@ -1787,7 +1787,7 @@
         <v>45</v>
       </c>
       <c r="C87">
-        <v>78.98</v>
+        <v>-78.98</v>
       </c>
       <c r="D87" t="s">
         <v>62</v>
@@ -1801,7 +1801,7 @@
         <v>56</v>
       </c>
       <c r="C88">
-        <v>190.89</v>
+        <v>-190.89</v>
       </c>
       <c r="D88" t="s">
         <v>66</v>
@@ -1815,7 +1815,7 @@
         <v>48</v>
       </c>
       <c r="C89">
-        <v>459.97</v>
+        <v>-459.97</v>
       </c>
       <c r="D89" t="s">
         <v>65</v>
@@ -1829,7 +1829,7 @@
         <v>49</v>
       </c>
       <c r="C90">
-        <v>18.33</v>
+        <v>-18.33</v>
       </c>
       <c r="D90" t="s">
         <v>61</v>
@@ -1843,7 +1843,7 @@
         <v>48</v>
       </c>
       <c r="C91">
-        <v>52.76</v>
+        <v>-52.76</v>
       </c>
       <c r="D91" t="s">
         <v>65</v>
@@ -1885,7 +1885,7 @@
         <v>42</v>
       </c>
       <c r="C94">
-        <v>509.1</v>
+        <v>-509.1</v>
       </c>
       <c r="D94" t="s">
         <v>63</v>
@@ -1899,7 +1899,7 @@
         <v>52</v>
       </c>
       <c r="C95">
-        <v>383.35</v>
+        <v>-383.35</v>
       </c>
       <c r="D95" t="s">
         <v>63</v>
@@ -1913,7 +1913,7 @@
         <v>38</v>
       </c>
       <c r="C96">
-        <v>3.71</v>
+        <v>-3.71</v>
       </c>
       <c r="D96" t="s">
         <v>61</v>
@@ -1927,7 +1927,7 @@
         <v>36</v>
       </c>
       <c r="C97">
-        <v>126.31</v>
+        <v>-126.31</v>
       </c>
       <c r="D97" t="s">
         <v>59</v>
@@ -1941,7 +1941,7 @@
         <v>42</v>
       </c>
       <c r="C98">
-        <v>99.81999999999999</v>
+        <v>-99.81999999999999</v>
       </c>
       <c r="D98" t="s">
         <v>63</v>
@@ -1983,7 +1983,7 @@
         <v>41</v>
       </c>
       <c r="C101">
-        <v>283.16</v>
+        <v>-283.16</v>
       </c>
       <c r="D101" t="s">
         <v>62</v>
@@ -1997,7 +1997,7 @@
         <v>48</v>
       </c>
       <c r="C102">
-        <v>20.91</v>
+        <v>-20.91</v>
       </c>
       <c r="D102" t="s">
         <v>65</v>
@@ -2011,7 +2011,7 @@
         <v>47</v>
       </c>
       <c r="C103">
-        <v>144.34</v>
+        <v>-144.34</v>
       </c>
       <c r="D103" t="s">
         <v>66</v>
@@ -2025,7 +2025,7 @@
         <v>58</v>
       </c>
       <c r="C104">
-        <v>15.49</v>
+        <v>-15.49</v>
       </c>
       <c r="D104" t="s">
         <v>66</v>
@@ -2053,7 +2053,7 @@
         <v>48</v>
       </c>
       <c r="C106">
-        <v>147.84</v>
+        <v>-147.84</v>
       </c>
       <c r="D106" t="s">
         <v>65</v>
@@ -2067,7 +2067,7 @@
         <v>42</v>
       </c>
       <c r="C107">
-        <v>685.54</v>
+        <v>-685.54</v>
       </c>
       <c r="D107" t="s">
         <v>63</v>
@@ -2081,7 +2081,7 @@
         <v>41</v>
       </c>
       <c r="C108">
-        <v>117.17</v>
+        <v>-117.17</v>
       </c>
       <c r="D108" t="s">
         <v>62</v>
@@ -2095,7 +2095,7 @@
         <v>40</v>
       </c>
       <c r="C109">
-        <v>37.57</v>
+        <v>-37.57</v>
       </c>
       <c r="D109" t="s">
         <v>61</v>
@@ -2109,7 +2109,7 @@
         <v>46</v>
       </c>
       <c r="C110">
-        <v>194.24</v>
+        <v>-194.24</v>
       </c>
       <c r="D110" t="s">
         <v>65</v>
@@ -2123,7 +2123,7 @@
         <v>54</v>
       </c>
       <c r="C111">
-        <v>58.86</v>
+        <v>-58.86</v>
       </c>
       <c r="D111" t="s">
         <v>59</v>
@@ -2137,7 +2137,7 @@
         <v>36</v>
       </c>
       <c r="C112">
-        <v>101.25</v>
+        <v>-101.25</v>
       </c>
       <c r="D112" t="s">
         <v>59</v>
@@ -2151,7 +2151,7 @@
         <v>54</v>
       </c>
       <c r="C113">
-        <v>146.6</v>
+        <v>-146.6</v>
       </c>
       <c r="D113" t="s">
         <v>59</v>
@@ -2165,7 +2165,7 @@
         <v>52</v>
       </c>
       <c r="C114">
-        <v>30.34</v>
+        <v>-30.34</v>
       </c>
       <c r="D114" t="s">
         <v>63</v>
@@ -2207,7 +2207,7 @@
         <v>57</v>
       </c>
       <c r="C117">
-        <v>238.57</v>
+        <v>-238.57</v>
       </c>
       <c r="D117" t="s">
         <v>62</v>
@@ -2221,7 +2221,7 @@
         <v>42</v>
       </c>
       <c r="C118">
-        <v>928.09</v>
+        <v>-928.09</v>
       </c>
       <c r="D118" t="s">
         <v>63</v>
@@ -2235,7 +2235,7 @@
         <v>53</v>
       </c>
       <c r="C119">
-        <v>76.20999999999999</v>
+        <v>-76.20999999999999</v>
       </c>
       <c r="D119" t="s">
         <v>60</v>
@@ -2249,7 +2249,7 @@
         <v>38</v>
       </c>
       <c r="C120">
-        <v>40.65</v>
+        <v>-40.65</v>
       </c>
       <c r="D120" t="s">
         <v>61</v>
@@ -2263,7 +2263,7 @@
         <v>47</v>
       </c>
       <c r="C121">
-        <v>86.56</v>
+        <v>-86.56</v>
       </c>
       <c r="D121" t="s">
         <v>66</v>
@@ -2277,7 +2277,7 @@
         <v>39</v>
       </c>
       <c r="C122">
-        <v>46.77</v>
+        <v>-46.77</v>
       </c>
       <c r="D122" t="s">
         <v>60</v>
@@ -2291,7 +2291,7 @@
         <v>38</v>
       </c>
       <c r="C123">
-        <v>14.39</v>
+        <v>-14.39</v>
       </c>
       <c r="D123" t="s">
         <v>61</v>
@@ -2305,7 +2305,7 @@
         <v>56</v>
       </c>
       <c r="C124">
-        <v>116.55</v>
+        <v>-116.55</v>
       </c>
       <c r="D124" t="s">
         <v>66</v>
@@ -2319,7 +2319,7 @@
         <v>56</v>
       </c>
       <c r="C125">
-        <v>183.16</v>
+        <v>-183.16</v>
       </c>
       <c r="D125" t="s">
         <v>66</v>
@@ -2333,7 +2333,7 @@
         <v>53</v>
       </c>
       <c r="C126">
-        <v>98.70999999999999</v>
+        <v>-98.70999999999999</v>
       </c>
       <c r="D126" t="s">
         <v>60</v>
@@ -2347,7 +2347,7 @@
         <v>58</v>
       </c>
       <c r="C127">
-        <v>45.87</v>
+        <v>-45.87</v>
       </c>
       <c r="D127" t="s">
         <v>66</v>
@@ -2361,7 +2361,7 @@
         <v>40</v>
       </c>
       <c r="C128">
-        <v>27.2</v>
+        <v>-27.2</v>
       </c>
       <c r="D128" t="s">
         <v>61</v>
@@ -2375,7 +2375,7 @@
         <v>48</v>
       </c>
       <c r="C129">
-        <v>433.84</v>
+        <v>-433.84</v>
       </c>
       <c r="D129" t="s">
         <v>65</v>
@@ -2389,7 +2389,7 @@
         <v>39</v>
       </c>
       <c r="C130">
-        <v>67.48</v>
+        <v>-67.48</v>
       </c>
       <c r="D130" t="s">
         <v>60</v>
@@ -2403,7 +2403,7 @@
         <v>50</v>
       </c>
       <c r="C131">
-        <v>54.97</v>
+        <v>-54.97</v>
       </c>
       <c r="D131" t="s">
         <v>65</v>
@@ -2417,7 +2417,7 @@
         <v>36</v>
       </c>
       <c r="C132">
-        <v>113.1</v>
+        <v>-113.1</v>
       </c>
       <c r="D132" t="s">
         <v>59</v>
@@ -2431,7 +2431,7 @@
         <v>41</v>
       </c>
       <c r="C133">
-        <v>40.37</v>
+        <v>-40.37</v>
       </c>
       <c r="D133" t="s">
         <v>62</v>
@@ -2445,7 +2445,7 @@
         <v>46</v>
       </c>
       <c r="C134">
-        <v>281.09</v>
+        <v>-281.09</v>
       </c>
       <c r="D134" t="s">
         <v>65</v>
@@ -2459,7 +2459,7 @@
         <v>51</v>
       </c>
       <c r="C135">
-        <v>873.1799999999999</v>
+        <v>-873.1799999999999</v>
       </c>
       <c r="D135" t="s">
         <v>63</v>
@@ -2487,7 +2487,7 @@
         <v>40</v>
       </c>
       <c r="C137">
-        <v>39.21</v>
+        <v>-39.21</v>
       </c>
       <c r="D137" t="s">
         <v>61</v>
@@ -2501,7 +2501,7 @@
         <v>37</v>
       </c>
       <c r="C138">
-        <v>84.94</v>
+        <v>-84.94</v>
       </c>
       <c r="D138" t="s">
         <v>60</v>
@@ -2515,7 +2515,7 @@
         <v>41</v>
       </c>
       <c r="C139">
-        <v>262.37</v>
+        <v>-262.37</v>
       </c>
       <c r="D139" t="s">
         <v>62</v>
@@ -2529,7 +2529,7 @@
         <v>46</v>
       </c>
       <c r="C140">
-        <v>174.05</v>
+        <v>-174.05</v>
       </c>
       <c r="D140" t="s">
         <v>65</v>
@@ -2543,7 +2543,7 @@
         <v>36</v>
       </c>
       <c r="C141">
-        <v>144.57</v>
+        <v>-144.57</v>
       </c>
       <c r="D141" t="s">
         <v>59</v>
@@ -2557,7 +2557,7 @@
         <v>56</v>
       </c>
       <c r="C142">
-        <v>151.67</v>
+        <v>-151.67</v>
       </c>
       <c r="D142" t="s">
         <v>66</v>
@@ -2571,7 +2571,7 @@
         <v>52</v>
       </c>
       <c r="C143">
-        <v>931.28</v>
+        <v>-931.28</v>
       </c>
       <c r="D143" t="s">
         <v>63</v>
@@ -2585,7 +2585,7 @@
         <v>58</v>
       </c>
       <c r="C144">
-        <v>144.34</v>
+        <v>-144.34</v>
       </c>
       <c r="D144" t="s">
         <v>66</v>
@@ -2599,7 +2599,7 @@
         <v>49</v>
       </c>
       <c r="C145">
-        <v>14.54</v>
+        <v>-14.54</v>
       </c>
       <c r="D145" t="s">
         <v>61</v>
@@ -2613,7 +2613,7 @@
         <v>54</v>
       </c>
       <c r="C146">
-        <v>98.59</v>
+        <v>-98.59</v>
       </c>
       <c r="D146" t="s">
         <v>59</v>
@@ -2641,7 +2641,7 @@
         <v>52</v>
       </c>
       <c r="C148">
-        <v>511.38</v>
+        <v>-511.38</v>
       </c>
       <c r="D148" t="s">
         <v>63</v>
@@ -2669,7 +2669,7 @@
         <v>46</v>
       </c>
       <c r="C150">
-        <v>16.76</v>
+        <v>-16.76</v>
       </c>
       <c r="D150" t="s">
         <v>65</v>
@@ -2683,7 +2683,7 @@
         <v>47</v>
       </c>
       <c r="C151">
-        <v>75.73999999999999</v>
+        <v>-75.73999999999999</v>
       </c>
       <c r="D151" t="s">
         <v>66</v>
@@ -2697,7 +2697,7 @@
         <v>51</v>
       </c>
       <c r="C152">
-        <v>842.37</v>
+        <v>-842.37</v>
       </c>
       <c r="D152" t="s">
         <v>63</v>
@@ -2711,7 +2711,7 @@
         <v>49</v>
       </c>
       <c r="C153">
-        <v>34.42</v>
+        <v>-34.42</v>
       </c>
       <c r="D153" t="s">
         <v>61</v>
@@ -2725,7 +2725,7 @@
         <v>52</v>
       </c>
       <c r="C154">
-        <v>826.96</v>
+        <v>-826.96</v>
       </c>
       <c r="D154" t="s">
         <v>63</v>
@@ -2753,7 +2753,7 @@
         <v>53</v>
       </c>
       <c r="C156">
-        <v>58.62</v>
+        <v>-58.62</v>
       </c>
       <c r="D156" t="s">
         <v>60</v>
@@ -2767,7 +2767,7 @@
         <v>50</v>
       </c>
       <c r="C157">
-        <v>86.81</v>
+        <v>-86.81</v>
       </c>
       <c r="D157" t="s">
         <v>65</v>
@@ -2781,7 +2781,7 @@
         <v>50</v>
       </c>
       <c r="C158">
-        <v>408.71</v>
+        <v>-408.71</v>
       </c>
       <c r="D158" t="s">
         <v>65</v>
@@ -2795,7 +2795,7 @@
         <v>57</v>
       </c>
       <c r="C159">
-        <v>170.46</v>
+        <v>-170.46</v>
       </c>
       <c r="D159" t="s">
         <v>62</v>
@@ -2809,7 +2809,7 @@
         <v>45</v>
       </c>
       <c r="C160">
-        <v>149.21</v>
+        <v>-149.21</v>
       </c>
       <c r="D160" t="s">
         <v>62</v>
@@ -2823,7 +2823,7 @@
         <v>42</v>
       </c>
       <c r="C161">
-        <v>509.68</v>
+        <v>-509.68</v>
       </c>
       <c r="D161" t="s">
         <v>63</v>
@@ -2837,7 +2837,7 @@
         <v>57</v>
       </c>
       <c r="C162">
-        <v>244.35</v>
+        <v>-244.35</v>
       </c>
       <c r="D162" t="s">
         <v>62</v>
@@ -2851,7 +2851,7 @@
         <v>42</v>
       </c>
       <c r="C163">
-        <v>64.04000000000001</v>
+        <v>-64.04000000000001</v>
       </c>
       <c r="D163" t="s">
         <v>63</v>
@@ -2865,7 +2865,7 @@
         <v>41</v>
       </c>
       <c r="C164">
-        <v>186.33</v>
+        <v>-186.33</v>
       </c>
       <c r="D164" t="s">
         <v>62</v>
@@ -2879,7 +2879,7 @@
         <v>49</v>
       </c>
       <c r="C165">
-        <v>31.57</v>
+        <v>-31.57</v>
       </c>
       <c r="D165" t="s">
         <v>61</v>
@@ -2893,7 +2893,7 @@
         <v>56</v>
       </c>
       <c r="C166">
-        <v>184.01</v>
+        <v>-184.01</v>
       </c>
       <c r="D166" t="s">
         <v>66</v>
@@ -2907,7 +2907,7 @@
         <v>46</v>
       </c>
       <c r="C167">
-        <v>269.42</v>
+        <v>-269.42</v>
       </c>
       <c r="D167" t="s">
         <v>65</v>
@@ -2921,7 +2921,7 @@
         <v>36</v>
       </c>
       <c r="C168">
-        <v>38.02</v>
+        <v>-38.02</v>
       </c>
       <c r="D168" t="s">
         <v>59</v>
@@ -2935,7 +2935,7 @@
         <v>56</v>
       </c>
       <c r="C169">
-        <v>178.2</v>
+        <v>-178.2</v>
       </c>
       <c r="D169" t="s">
         <v>66</v>
@@ -2949,7 +2949,7 @@
         <v>35</v>
       </c>
       <c r="C170">
-        <v>136.41</v>
+        <v>-136.41</v>
       </c>
       <c r="D170" t="s">
         <v>59</v>
@@ -2963,7 +2963,7 @@
         <v>56</v>
       </c>
       <c r="C171">
-        <v>60.53</v>
+        <v>-60.53</v>
       </c>
       <c r="D171" t="s">
         <v>66</v>
@@ -2977,7 +2977,7 @@
         <v>45</v>
       </c>
       <c r="C172">
-        <v>287.75</v>
+        <v>-287.75</v>
       </c>
       <c r="D172" t="s">
         <v>62</v>
@@ -2991,7 +2991,7 @@
         <v>48</v>
       </c>
       <c r="C173">
-        <v>150.72</v>
+        <v>-150.72</v>
       </c>
       <c r="D173" t="s">
         <v>65</v>
@@ -3005,7 +3005,7 @@
         <v>53</v>
       </c>
       <c r="C174">
-        <v>98.68000000000001</v>
+        <v>-98.68000000000001</v>
       </c>
       <c r="D174" t="s">
         <v>60</v>
@@ -3033,7 +3033,7 @@
         <v>47</v>
       </c>
       <c r="C176">
-        <v>141.79</v>
+        <v>-141.79</v>
       </c>
       <c r="D176" t="s">
         <v>66</v>
@@ -3047,7 +3047,7 @@
         <v>47</v>
       </c>
       <c r="C177">
-        <v>99.76000000000001</v>
+        <v>-99.76000000000001</v>
       </c>
       <c r="D177" t="s">
         <v>66</v>
@@ -3075,7 +3075,7 @@
         <v>58</v>
       </c>
       <c r="C179">
-        <v>188.55</v>
+        <v>-188.55</v>
       </c>
       <c r="D179" t="s">
         <v>66</v>
@@ -3089,7 +3089,7 @@
         <v>36</v>
       </c>
       <c r="C180">
-        <v>97.40000000000001</v>
+        <v>-97.40000000000001</v>
       </c>
       <c r="D180" t="s">
         <v>59</v>
@@ -3103,7 +3103,7 @@
         <v>46</v>
       </c>
       <c r="C181">
-        <v>293.11</v>
+        <v>-293.11</v>
       </c>
       <c r="D181" t="s">
         <v>65</v>
@@ -3145,7 +3145,7 @@
         <v>47</v>
       </c>
       <c r="C184">
-        <v>109.22</v>
+        <v>-109.22</v>
       </c>
       <c r="D184" t="s">
         <v>66</v>
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="C185">
-        <v>272.8</v>
+        <v>-272.8</v>
       </c>
       <c r="D185" t="s">
         <v>62</v>
@@ -3173,7 +3173,7 @@
         <v>36</v>
       </c>
       <c r="C186">
-        <v>98.03</v>
+        <v>-98.03</v>
       </c>
       <c r="D186" t="s">
         <v>59</v>
@@ -3187,7 +3187,7 @@
         <v>58</v>
       </c>
       <c r="C187">
-        <v>111.92</v>
+        <v>-111.92</v>
       </c>
       <c r="D187" t="s">
         <v>66</v>
@@ -3201,7 +3201,7 @@
         <v>54</v>
       </c>
       <c r="C188">
-        <v>44.79</v>
+        <v>-44.79</v>
       </c>
       <c r="D188" t="s">
         <v>59</v>
@@ -3215,7 +3215,7 @@
         <v>42</v>
       </c>
       <c r="C189">
-        <v>302.59</v>
+        <v>-302.59</v>
       </c>
       <c r="D189" t="s">
         <v>63</v>
@@ -3229,7 +3229,7 @@
         <v>42</v>
       </c>
       <c r="C190">
-        <v>213.69</v>
+        <v>-213.69</v>
       </c>
       <c r="D190" t="s">
         <v>63</v>
@@ -3243,7 +3243,7 @@
         <v>54</v>
       </c>
       <c r="C191">
-        <v>28.82</v>
+        <v>-28.82</v>
       </c>
       <c r="D191" t="s">
         <v>59</v>
@@ -3271,7 +3271,7 @@
         <v>41</v>
       </c>
       <c r="C193">
-        <v>66.33</v>
+        <v>-66.33</v>
       </c>
       <c r="D193" t="s">
         <v>62</v>
@@ -3285,7 +3285,7 @@
         <v>56</v>
       </c>
       <c r="C194">
-        <v>70.54000000000001</v>
+        <v>-70.54000000000001</v>
       </c>
       <c r="D194" t="s">
         <v>66</v>
@@ -3299,7 +3299,7 @@
         <v>42</v>
       </c>
       <c r="C195">
-        <v>454.51</v>
+        <v>-454.51</v>
       </c>
       <c r="D195" t="s">
         <v>63</v>
@@ -3327,7 +3327,7 @@
         <v>36</v>
       </c>
       <c r="C197">
-        <v>118.13</v>
+        <v>-118.13</v>
       </c>
       <c r="D197" t="s">
         <v>59</v>
@@ -3341,7 +3341,7 @@
         <v>53</v>
       </c>
       <c r="C198">
-        <v>58.93</v>
+        <v>-58.93</v>
       </c>
       <c r="D198" t="s">
         <v>60</v>
@@ -3355,7 +3355,7 @@
         <v>57</v>
       </c>
       <c r="C199">
-        <v>82.89</v>
+        <v>-82.89</v>
       </c>
       <c r="D199" t="s">
         <v>62</v>
@@ -3369,7 +3369,7 @@
         <v>37</v>
       </c>
       <c r="C200">
-        <v>38.57</v>
+        <v>-38.57</v>
       </c>
       <c r="D200" t="s">
         <v>60</v>
@@ -3383,7 +3383,7 @@
         <v>54</v>
       </c>
       <c r="C201">
-        <v>27.69</v>
+        <v>-27.69</v>
       </c>
       <c r="D201" t="s">
         <v>59</v>
